--- a/public/exports/29188599.xlsx
+++ b/public/exports/29188599.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -14764,12 +14764,12 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592261</t>
+          <t xml:space="preserve">311592264</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -14839,12 +14839,12 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592262</t>
+          <t xml:space="preserve">311592264</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -14914,12 +14914,12 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592263</t>
+          <t xml:space="preserve">311592264</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -14989,12 +14989,12 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592263</t>
+          <t xml:space="preserve">311592264</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -16339,7 +16339,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -16489,12 +16489,12 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615356</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -16564,12 +16564,12 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615354</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -16639,7 +16639,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -16789,7 +16789,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -16864,7 +16864,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -16939,7 +16939,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -17014,7 +17014,7 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -17239,7 +17239,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615357</t>
+          <t xml:space="preserve">311615360</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">

--- a/public/exports/29188599.xlsx
+++ b/public/exports/29188599.xlsx
@@ -14764,12 +14764,12 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592264</t>
+          <t xml:space="preserve">311592261</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -14839,12 +14839,12 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592264</t>
+          <t xml:space="preserve">311592262</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -14914,12 +14914,12 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592264</t>
+          <t xml:space="preserve">311592263</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -14989,12 +14989,12 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592264</t>
+          <t xml:space="preserve">311592263</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -16564,12 +16564,12 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615354</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615359</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">

--- a/public/exports/29188599.xlsx
+++ b/public/exports/29188599.xlsx
@@ -16339,7 +16339,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -16489,12 +16489,12 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615356</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615359</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -16789,7 +16789,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -16864,7 +16864,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -16939,7 +16939,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -17014,7 +17014,7 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -17239,7 +17239,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311615360</t>
+          <t xml:space="preserve">311615357</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
